--- a/Lopsided Productions Issues Log.xlsx
+++ b/Lopsided Productions Issues Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdigu\Desktop\Insomniac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762D50C7-D03B-40B8-B771-D7CFB518D941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59847D6D-508A-45ED-AAE8-4DF27041CE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15795" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{E426D4A3-675A-4749-AD97-AF7CA7903CDF}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Issues Quantification" sheetId="7" r:id="rId1"/>
     <sheet name="Issues" sheetId="3" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -153,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="160">
   <si>
     <t>Ref #</t>
   </si>
@@ -491,9 +494,6 @@
     <t>Focus on MVP (Minimum Viable Product)</t>
   </si>
   <si>
-    <t>Design will be regularly reviewed and any deviations will be documented as a risk. Deviations will also be tracked on the Decision Log and a Crused if needed.</t>
-  </si>
-  <si>
     <t>Add instructions at the start screen for the user to learn the game rules.</t>
   </si>
   <si>
@@ -542,12 +542,6 @@
     <t>This risk will be reviewed during the coding and testing process. Results will be documented, and corrections will be added to the coding tasks.</t>
   </si>
   <si>
-    <t>Structured event logic will be developed and reviewed during the coding process. Results will be documente,d and corrections will be added to the coding tasks.</t>
-  </si>
-  <si>
-    <t>J,N,T</t>
-  </si>
-  <si>
     <t>Last Update: 5/12/2026</t>
   </si>
   <si>
@@ -618,6 +612,33 @@
   </si>
   <si>
     <t>Lopsided Productions Project Issues</t>
+  </si>
+  <si>
+    <t>Jessica, Nick, Tom</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Integration of meter and threat tested and complete.</t>
+  </si>
+  <si>
+    <t>Tested</t>
+  </si>
+  <si>
+    <t>No changes made to project scope.</t>
+  </si>
+  <si>
+    <t>Structured event logic will be developed and reviewed during the coding process. Results will be documented and corrections will be added to the coding tasks.</t>
+  </si>
+  <si>
+    <t>Included in test plan</t>
+  </si>
+  <si>
+    <t>Design will be regularly reviewed and any deviations will be documented as a risk. Deviations will also be tracked on the Decision Log and added if needed.</t>
+  </si>
+  <si>
+    <t>No deviations noted.</t>
   </si>
 </sst>
 </file>
@@ -879,7 +900,43 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8A8C821D-C0A4-4E8C-8E69-877CD3B7D532}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="19">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -903,40 +960,26 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -976,21 +1019,45 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Issues Quantification"/>
+      <sheetName val="Issues"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L25" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L25" totalsRowShown="0" headerRowDxfId="18" dataDxfId="0">
   <autoFilter ref="B3:L25" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Risk Name" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Risk Description" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Risk Response Plan" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Risk Name" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Risk Description" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Risk Response Plan" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="3">
+      <calculatedColumnFormula>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+(1 to 10)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1700,7 +1767,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="25" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -1715,7 +1782,7 @@
     </row>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
@@ -1765,7 +1832,7 @@
     </row>
     <row r="4" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>59</v>
@@ -1774,10 +1841,10 @@
         <v>60</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G4" s="20">
         <v>8</v>
@@ -1789,20 +1856,22 @@
         <v>1</v>
       </c>
       <c r="J4" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>72</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L4" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="5" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B5" s="16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>62</v>
@@ -1811,10 +1880,10 @@
         <v>63</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G5" s="20">
         <v>7</v>
@@ -1826,20 +1895,22 @@
         <v>1</v>
       </c>
       <c r="J5" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>56</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="6" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>64</v>
@@ -1848,10 +1919,10 @@
         <v>65</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G6" s="20">
         <v>6</v>
@@ -1863,20 +1934,22 @@
         <v>1</v>
       </c>
       <c r="J6" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>54</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="7" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B7" s="16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>66</v>
@@ -1885,10 +1958,10 @@
         <v>67</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G7" s="20">
         <v>7</v>
@@ -1900,20 +1973,22 @@
         <v>1</v>
       </c>
       <c r="J7" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>63</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L7" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="8" spans="2:12" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>68</v>
@@ -1925,7 +2000,7 @@
         <v>108</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G8" s="20">
         <v>6</v>
@@ -1937,20 +2012,22 @@
         <v>3</v>
       </c>
       <c r="J8" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>126</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="18"/>
+        <v>152</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="9" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>70</v>
@@ -1962,7 +2039,7 @@
         <v>107</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G9" s="20">
         <v>3</v>
@@ -1974,20 +2051,20 @@
         <v>2</v>
       </c>
       <c r="J9" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>48</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L9" s="18"/>
     </row>
     <row r="10" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>72</v>
@@ -1999,7 +2076,7 @@
         <v>106</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G10" s="20">
         <v>5</v>
@@ -2011,20 +2088,20 @@
         <v>3</v>
       </c>
       <c r="J10" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>105</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L10" s="18"/>
     </row>
     <row r="11" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>74</v>
@@ -2033,10 +2110,10 @@
         <v>75</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G11" s="20">
         <v>5</v>
@@ -2048,20 +2125,20 @@
         <v>2</v>
       </c>
       <c r="J11" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>60</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>76</v>
@@ -2070,10 +2147,10 @@
         <v>77</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G12" s="20">
         <v>3</v>
@@ -2085,20 +2162,20 @@
         <v>4</v>
       </c>
       <c r="J12" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L12" s="18"/>
     </row>
     <row r="13" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B13" s="16" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>78</v>
@@ -2107,10 +2184,10 @@
         <v>79</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G13" s="20">
         <v>4</v>
@@ -2122,20 +2199,20 @@
         <v>2</v>
       </c>
       <c r="J13" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>64</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L13" s="18"/>
     </row>
     <row r="14" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="16" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>80</v>
@@ -2144,10 +2221,10 @@
         <v>81</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G14" s="20">
         <v>3</v>
@@ -2159,20 +2236,20 @@
         <v>4</v>
       </c>
       <c r="J14" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L14" s="18"/>
     </row>
     <row r="15" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>82</v>
@@ -2181,10 +2258,10 @@
         <v>83</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G15" s="20">
         <v>5</v>
@@ -2196,20 +2273,20 @@
         <v>3</v>
       </c>
       <c r="J15" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>120</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L15" s="18"/>
     </row>
-    <row r="16" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>84</v>
@@ -2218,10 +2295,10 @@
         <v>85</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G16" s="20">
         <v>5</v>
@@ -2233,20 +2310,20 @@
         <v>2</v>
       </c>
       <c r="J16" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L16" s="18"/>
     </row>
     <row r="17" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>86</v>
@@ -2255,10 +2332,10 @@
         <v>87</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G17" s="20">
         <v>5</v>
@@ -2270,20 +2347,20 @@
         <v>2</v>
       </c>
       <c r="J17" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>80</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L17" s="18"/>
     </row>
     <row r="18" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>88</v>
@@ -2292,10 +2369,10 @@
         <v>89</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G18" s="20">
         <v>4</v>
@@ -2307,32 +2384,32 @@
         <v>4</v>
       </c>
       <c r="J18" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L18" s="18"/>
     </row>
     <row r="19" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D19" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>117</v>
-      </c>
       <c r="F19" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G19" s="20">
         <v>3</v>
@@ -2344,20 +2421,20 @@
         <v>3</v>
       </c>
       <c r="J19" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>54</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>91</v>
@@ -2366,10 +2443,10 @@
         <v>92</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G20" s="20">
         <v>4</v>
@@ -2381,20 +2458,20 @@
         <v>3</v>
       </c>
       <c r="J20" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>108</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>93</v>
@@ -2403,10 +2480,10 @@
         <v>94</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G21" s="20">
         <v>4</v>
@@ -2418,20 +2495,20 @@
         <v>3</v>
       </c>
       <c r="J21" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L21" s="18"/>
     </row>
     <row r="22" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>95</v>
@@ -2440,10 +2517,10 @@
         <v>96</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G22" s="20">
         <v>3</v>
@@ -2455,20 +2532,20 @@
         <v>4</v>
       </c>
       <c r="J22" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L22" s="18"/>
     </row>
     <row r="23" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>97</v>
@@ -2480,7 +2557,7 @@
         <v>110</v>
       </c>
       <c r="F23" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G23" s="20">
         <v>5</v>
@@ -2492,20 +2569,20 @@
         <v>2</v>
       </c>
       <c r="J23" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="L23" s="18"/>
     </row>
     <row r="24" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>99</v>
@@ -2517,7 +2594,7 @@
         <v>109</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G24" s="20">
         <v>4</v>
@@ -2529,19 +2606,22 @@
         <v>3</v>
       </c>
       <c r="J24" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K24" s="21" t="s">
         <v>61</v>
       </c>
+      <c r="L24" s="23" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="25" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B25" s="20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>101</v>
@@ -2550,10 +2630,10 @@
         <v>102</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="G25" s="20">
         <v>5</v>
@@ -2565,14 +2645,17 @@
         <v>2</v>
       </c>
       <c r="J25" s="20">
-        <f>Table1[[#This Row],[Probability
-(1 to 10)]]*Table1[[#This Row],[Severity
-(1 to 10)]]*Table1[[#This Row],[Detection
+        <f>[1]!Table1[[#This Row],[Probability
+(1 to 10)]]*[1]!Table1[[#This Row],[Severity
+(1 to 10)]]*[1]!Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K25" s="21" t="s">
-        <v>61</v>
+        <v>152</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
@@ -2586,14 +2669,14 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="J4:J25">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="between">
       <formula>101</formula>
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
       <formula>101</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Lopsided Productions Issues Log.xlsx
+++ b/Lopsided Productions Issues Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdigu\Desktop\Insomniac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59847D6D-508A-45ED-AAE8-4DF27041CE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4372711D-1AEA-48A3-9450-3ECDDEA0CC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15795" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{E426D4A3-675A-4749-AD97-AF7CA7903CDF}"/>
   </bookViews>
@@ -16,9 +16,6 @@
     <sheet name="Issues Quantification" sheetId="7" r:id="rId1"/>
     <sheet name="Issues" sheetId="3" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -156,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="193">
   <si>
     <t>Ref #</t>
   </si>
@@ -170,12 +167,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>Risk Description</t>
-  </si>
-  <si>
-    <t>Risk Response Plan</t>
-  </si>
-  <si>
     <t>RPN</t>
   </si>
   <si>
@@ -330,9 +321,6 @@
   </si>
   <si>
     <t>Almost Certain</t>
-  </si>
-  <si>
-    <t>Risk Name</t>
   </si>
   <si>
     <t>Core Gameplay Logic Failure</t>
@@ -542,9 +530,6 @@
     <t>This risk will be reviewed during the coding and testing process. Results will be documented, and corrections will be added to the coding tasks.</t>
   </si>
   <si>
-    <t>Last Update: 5/12/2026</t>
-  </si>
-  <si>
     <t>IL01</t>
   </si>
   <si>
@@ -639,6 +624,117 @@
   </si>
   <si>
     <t>No deviations noted.</t>
+  </si>
+  <si>
+    <t>Issue Name</t>
+  </si>
+  <si>
+    <t>Issue Description</t>
+  </si>
+  <si>
+    <t>Response Plan</t>
+  </si>
+  <si>
+    <t>IL23</t>
+  </si>
+  <si>
+    <t>IL24</t>
+  </si>
+  <si>
+    <t>IL25</t>
+  </si>
+  <si>
+    <t>IL26</t>
+  </si>
+  <si>
+    <t>Missing or unclear submission requirements</t>
+  </si>
+  <si>
+    <t>Team unclear where deliverables must be submitted (Discussion Board vs Blackboard).</t>
+  </si>
+  <si>
+    <t>Limited team availability</t>
+  </si>
+  <si>
+    <t>Personal events and work meetings may delay project activities.</t>
+  </si>
+  <si>
+    <t>Final release stability risk</t>
+  </si>
+  <si>
+    <t>Late-stage gameplay and save system changes may introduce defects.</t>
+  </si>
+  <si>
+    <t>Gameplay clarity risk</t>
+  </si>
+  <si>
+    <t>Some testers requested clearer gameplay instructions.</t>
+  </si>
+  <si>
+    <t>Verify submission instructions and assign validation owner.</t>
+  </si>
+  <si>
+    <t>Maintain shared ownership and updated GitHub repository.</t>
+  </si>
+  <si>
+    <t>Perform regression testing and freeze features before release.</t>
+  </si>
+  <si>
+    <t>Add concise gameplay hints or startup instructions.</t>
+  </si>
+  <si>
+    <t>Tom</t>
+  </si>
+  <si>
+    <t>Nick</t>
+  </si>
+  <si>
+    <t>IL27</t>
+  </si>
+  <si>
+    <t>IL28</t>
+  </si>
+  <si>
+    <t>IL29</t>
+  </si>
+  <si>
+    <t>IL30</t>
+  </si>
+  <si>
+    <t>Submission location confusion</t>
+  </si>
+  <si>
+    <t>Unclear whether Proof of Concept required Blackboard submission in addition to Discussion Board.</t>
+  </si>
+  <si>
+    <t>Story sequence order missing</t>
+  </si>
+  <si>
+    <t>Story order accidentally removed after update.</t>
+  </si>
+  <si>
+    <t>GitHub issue tracker not maintained</t>
+  </si>
+  <si>
+    <t>Team uncertain whether GitHub Issues or Excel tracker was official.</t>
+  </si>
+  <si>
+    <t>Presentation coordination needed</t>
+  </si>
+  <si>
+    <t>Team needs rehearsal and coordination before final presentation.</t>
+  </si>
+  <si>
+    <t>Restore intended story sequence order.</t>
+  </si>
+  <si>
+    <t>Schedule practice session before presentation.</t>
+  </si>
+  <si>
+    <t>Team agreed to use Excel for Logs and are located on GitHub.</t>
+  </si>
+  <si>
+    <t>Last Update: 5/14/2026</t>
   </si>
 </sst>
 </file>
@@ -814,7 +910,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -895,47 +991,74 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{8A8C821D-C0A4-4E8C-8E69-877CD3B7D532}"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="27">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <fgColor rgb="FF00B050"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -982,6 +1105,39 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1019,45 +1175,26 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Issues Quantification"/>
-      <sheetName val="Issues"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L25" totalsRowShown="0" headerRowDxfId="18" dataDxfId="0">
-  <autoFilter ref="B3:L25" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}" name="Table1" displayName="Table1" ref="B3:L34" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="B3:L34" xr:uid="{F71E0ABB-2CB7-4F30-B614-D9D3F47E65F2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Risk Name" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Risk Description" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Risk Response Plan" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="3">
-      <calculatedColumnFormula>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+    <tableColumn id="1" xr3:uid="{736B15C0-0F35-48DB-84DE-CEEBE506D676}" name="Ref #" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{B3FFA252-2A18-4F52-93A6-87934BBA95B9}" name="Issue Name" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{E0DD0BBC-368D-42CC-AF91-AB2733085A76}" name="Issue Description" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{80E5263E-10D7-43F9-9EF0-114304CB78A4}" name="Response Plan" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{D6E73ED4-DD96-44AA-B965-D555E4A0C3A1}" name="Owner" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{29AEA3B4-518D-4AE6-AD8C-6AAF74220C48}" name="Probability_x000a_(1 to 10)" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{CEDADF23-4B40-4C9D-BCD7-700102FAD97A}" name="Severity_x000a_(1 to 10)" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{B2921CAE-A3B5-4A34-B3AA-FC083952FC9C}" name="Detection_x000a_(1 to 10)" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{B04E42AE-7EAB-4978-A905-E0027E6B4FE2}" name="RPN" dataDxfId="8">
+      <calculatedColumnFormula>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{C8C3B578-51C9-4026-993C-2C9CE708190B}" name="Status" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{E106A908-5D4E-4D05-AD4E-3176C7CB82CB}" name="Comments" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1374,7 +1511,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="29"/>
@@ -1384,21 +1521,21 @@
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>10</v>
@@ -1407,7 +1544,7 @@
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4">
         <v>9</v>
@@ -1415,10 +1552,10 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4">
         <v>8</v>
@@ -1427,7 +1564,7 @@
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4">
         <v>7</v>
@@ -1435,10 +1572,10 @@
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4">
         <v>6</v>
@@ -1447,7 +1584,7 @@
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4">
         <v>5</v>
@@ -1456,7 +1593,7 @@
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="4">
         <v>4</v>
@@ -1464,10 +1601,10 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4">
         <v>3</v>
@@ -1476,7 +1613,7 @@
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="4">
         <v>2</v>
@@ -1484,10 +1621,10 @@
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
@@ -1495,7 +1632,7 @@
     </row>
     <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="29"/>
@@ -1505,21 +1642,21 @@
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4">
         <v>10</v>
@@ -1527,10 +1664,10 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16" s="4">
         <v>9</v>
@@ -1538,10 +1675,10 @@
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C17" s="4">
         <v>8</v>
@@ -1549,10 +1686,10 @@
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4">
         <v>7</v>
@@ -1560,10 +1697,10 @@
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4">
         <v>6</v>
@@ -1571,10 +1708,10 @@
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" s="4">
         <v>5</v>
@@ -1582,10 +1719,10 @@
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C21" s="4">
         <v>4</v>
@@ -1593,10 +1730,10 @@
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C22" s="4">
         <v>3</v>
@@ -1604,10 +1741,10 @@
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" s="4">
         <v>2</v>
@@ -1615,10 +1752,10 @@
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
@@ -1627,7 +1764,7 @@
     <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A25" s="14"/>
       <c r="B25" s="27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="9"/>
@@ -1637,16 +1774,16 @@
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="4">
         <v>10</v>
@@ -1655,7 +1792,7 @@
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C28" s="4">
         <v>9</v>
@@ -1664,7 +1801,7 @@
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" s="4">
         <v>8</v>
@@ -1673,7 +1810,7 @@
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="4">
         <v>7</v>
@@ -1682,7 +1819,7 @@
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4">
         <v>6</v>
@@ -1691,7 +1828,7 @@
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4">
         <v>5</v>
@@ -1700,7 +1837,7 @@
     <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C33" s="4">
         <v>4</v>
@@ -1709,7 +1846,7 @@
     <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C34" s="4">
         <v>3</v>
@@ -1718,7 +1855,7 @@
     <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
@@ -1727,7 +1864,7 @@
     <row r="36" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -1751,7 +1888,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B1:L26"/>
+  <dimension ref="B1:L34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -1767,7 +1904,7 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="25" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -1782,7 +1919,7 @@
     </row>
     <row r="2" spans="2:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
-        <v>127</v>
+        <v>192</v>
       </c>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
@@ -1800,28 +1937,28 @@
         <v>0</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>4</v>
+        <v>157</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K3" s="13" t="s">
         <v>2</v>
@@ -1832,19 +1969,19 @@
     </row>
     <row r="4" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G4" s="20">
         <v>8</v>
@@ -1856,34 +1993,34 @@
         <v>1</v>
       </c>
       <c r="J4" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>72</v>
       </c>
       <c r="K4" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B5" s="16" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G5" s="20">
         <v>7</v>
@@ -1895,34 +2032,34 @@
         <v>1</v>
       </c>
       <c r="J5" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>56</v>
       </c>
       <c r="K5" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B6" s="16" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G6" s="20">
         <v>6</v>
@@ -1934,34 +2071,34 @@
         <v>1</v>
       </c>
       <c r="J6" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>54</v>
       </c>
       <c r="K6" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L6" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B7" s="16" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G7" s="20">
         <v>7</v>
@@ -1973,34 +2110,34 @@
         <v>1</v>
       </c>
       <c r="J7" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>63</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L7" s="19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="2:12" s="22" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="B8" s="16" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G8" s="20">
         <v>6</v>
@@ -2012,34 +2149,34 @@
         <v>3</v>
       </c>
       <c r="J8" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>126</v>
       </c>
       <c r="K8" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L8" s="19" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G9" s="20">
         <v>3</v>
@@ -2051,32 +2188,32 @@
         <v>2</v>
       </c>
       <c r="J9" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>48</v>
       </c>
       <c r="K9" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L9" s="18"/>
     </row>
     <row r="10" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G10" s="20">
         <v>5</v>
@@ -2088,32 +2225,32 @@
         <v>3</v>
       </c>
       <c r="J10" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>105</v>
       </c>
       <c r="K10" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L10" s="18"/>
     </row>
     <row r="11" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G11" s="20">
         <v>5</v>
@@ -2125,32 +2262,32 @@
         <v>2</v>
       </c>
       <c r="J11" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>60</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G12" s="20">
         <v>3</v>
@@ -2162,32 +2299,32 @@
         <v>4</v>
       </c>
       <c r="J12" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L12" s="18"/>
     </row>
     <row r="13" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B13" s="16" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G13" s="20">
         <v>4</v>
@@ -2199,32 +2336,32 @@
         <v>2</v>
       </c>
       <c r="J13" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>64</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L13" s="18"/>
     </row>
     <row r="14" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G14" s="20">
         <v>3</v>
@@ -2236,32 +2373,32 @@
         <v>4</v>
       </c>
       <c r="J14" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L14" s="18"/>
     </row>
     <row r="15" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G15" s="20">
         <v>5</v>
@@ -2273,32 +2410,32 @@
         <v>3</v>
       </c>
       <c r="J15" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>120</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L15" s="18"/>
     </row>
-    <row r="16" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G16" s="20">
         <v>5</v>
@@ -2310,32 +2447,32 @@
         <v>2</v>
       </c>
       <c r="J16" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L16" s="18"/>
     </row>
     <row r="17" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G17" s="20">
         <v>5</v>
@@ -2347,32 +2484,32 @@
         <v>2</v>
       </c>
       <c r="J17" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>80</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L17" s="18"/>
     </row>
     <row r="18" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G18" s="20">
         <v>4</v>
@@ -2384,32 +2521,32 @@
         <v>4</v>
       </c>
       <c r="J18" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L18" s="18"/>
     </row>
     <row r="19" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G19" s="20">
         <v>3</v>
@@ -2421,32 +2558,32 @@
         <v>3</v>
       </c>
       <c r="J19" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>54</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G20" s="20">
         <v>4</v>
@@ -2458,32 +2595,32 @@
         <v>3</v>
       </c>
       <c r="J20" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>108</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" s="22" customFormat="1" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F21" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G21" s="20">
         <v>4</v>
@@ -2495,32 +2632,32 @@
         <v>3</v>
       </c>
       <c r="J21" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L21" s="18"/>
     </row>
     <row r="22" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G22" s="20">
         <v>3</v>
@@ -2532,32 +2669,32 @@
         <v>4</v>
       </c>
       <c r="J22" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>96</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L22" s="18"/>
     </row>
     <row r="23" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>151</v>
       </c>
       <c r="G23" s="20">
         <v>5</v>
@@ -2569,32 +2706,32 @@
         <v>2</v>
       </c>
       <c r="J23" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L23" s="18"/>
     </row>
     <row r="24" spans="2:12" s="22" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="20" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G24" s="20">
         <v>4</v>
@@ -2606,34 +2743,34 @@
         <v>3</v>
       </c>
       <c r="J24" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>84</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="2:12" s="22" customFormat="1" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="B25" s="20" t="s">
-        <v>149</v>
+      <c r="B25" s="21" t="s">
+        <v>145</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G25" s="20">
         <v>5</v>
@@ -2645,22 +2782,333 @@
         <v>2</v>
       </c>
       <c r="J25" s="20">
-        <f>[1]!Table1[[#This Row],[Probability
-(1 to 10)]]*[1]!Table1[[#This Row],[Severity
-(1 to 10)]]*[1]!Table1[[#This Row],[Detection
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
 (1 to 10)]]</f>
         <v>70</v>
       </c>
       <c r="K25" s="21" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="L25" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B26" s="20" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
+      <c r="C26" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="20">
+        <v>5</v>
+      </c>
+      <c r="H26" s="20">
+        <v>5</v>
+      </c>
+      <c r="I26" s="20">
+        <v>5</v>
+      </c>
+      <c r="J26" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>125</v>
+      </c>
+      <c r="K26" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B27" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" s="20">
+        <v>5</v>
+      </c>
+      <c r="H27" s="20">
+        <v>5</v>
+      </c>
+      <c r="I27" s="20">
+        <v>5</v>
+      </c>
+      <c r="J27" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>125</v>
+      </c>
+      <c r="K27" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L27" s="18"/>
+    </row>
+    <row r="28" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B28" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="20">
+        <v>5</v>
+      </c>
+      <c r="H28" s="20">
+        <v>5</v>
+      </c>
+      <c r="I28" s="20">
+        <v>5</v>
+      </c>
+      <c r="J28" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>125</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L28" s="18"/>
+    </row>
+    <row r="29" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B29" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="20">
+        <v>3</v>
+      </c>
+      <c r="H29" s="20">
+        <v>5</v>
+      </c>
+      <c r="I29" s="20">
+        <v>5</v>
+      </c>
+      <c r="J29" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>75</v>
+      </c>
+      <c r="K29" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="18"/>
+    </row>
+    <row r="30" spans="2:12" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="B30" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30" s="20">
+        <v>3</v>
+      </c>
+      <c r="H30" s="20">
+        <v>5</v>
+      </c>
+      <c r="I30" s="20">
+        <v>5</v>
+      </c>
+      <c r="J30" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>75</v>
+      </c>
+      <c r="K30" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L30" s="18"/>
+    </row>
+    <row r="31" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B31" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="G31" s="20">
+        <v>3</v>
+      </c>
+      <c r="H31" s="20">
+        <v>3</v>
+      </c>
+      <c r="I31" s="20">
+        <v>5</v>
+      </c>
+      <c r="J31" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>45</v>
+      </c>
+      <c r="K31" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L31" s="18"/>
+    </row>
+    <row r="32" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B32" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G32" s="20">
+        <v>3</v>
+      </c>
+      <c r="H32" s="20">
+        <v>1</v>
+      </c>
+      <c r="I32" s="20">
+        <v>5</v>
+      </c>
+      <c r="J32" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>15</v>
+      </c>
+      <c r="K32" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="L32" s="18"/>
+    </row>
+    <row r="33" spans="2:12" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="B33" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G33" s="20">
+        <v>3</v>
+      </c>
+      <c r="H33" s="20">
+        <v>3</v>
+      </c>
+      <c r="I33" s="20">
+        <v>3</v>
+      </c>
+      <c r="J33" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>27</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="18"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="16"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20">
+        <f>Table1[[#This Row],[Probability
+(1 to 10)]]*Table1[[#This Row],[Severity
+(1 to 10)]]*Table1[[#This Row],[Detection
+(1 to 10)]]</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="20"/>
+      <c r="L34" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2668,16 +3116,21 @@
     <mergeCell ref="B2:L2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="J4:J25">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="J4:J34">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>101</formula>
       <formula>300</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="lessThan">
       <formula>101</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:K34">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Open"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions gridLines="1"/>
